--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="116">
   <si>
     <t>#</t>
   </si>
@@ -177,6 +177,66 @@
   </si>
   <si>
     <t>龙之血</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之怒*1</t>
+  </si>
+  <si>
+    <t>龙之怒</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之刀*1</t>
+  </si>
+  <si>
+    <t>龙之刀</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之杖*1</t>
+  </si>
+  <si>
+    <t>龙之杖</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之剑*1</t>
+  </si>
+  <si>
+    <t>龙之剑</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·白*1</t>
+  </si>
+  <si>
+    <t>神鉴·白</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·绿*1</t>
+  </si>
+  <si>
+    <t>神鉴·绿</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·蓝*1</t>
+  </si>
+  <si>
+    <t>神鉴·蓝</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·紫*1</t>
+  </si>
+  <si>
+    <t>神鉴·紫</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·橙*1</t>
+  </si>
+  <si>
+    <t>神鉴·橙</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·红*1</t>
+  </si>
+  <si>
+    <t>神鉴·红</t>
   </si>
   <si>
     <t>兑换特戒自选*1</t>
@@ -1323,17 +1383,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:N60"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2566371681416" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5044247787611" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1238938053097" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8761061946903" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.50442477876106" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5044247787611" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1722,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" ref="L14:L37" si="1">E14*F14</f>
+        <f>E14*F14</f>
         <v>15000</v>
       </c>
     </row>
@@ -1755,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="1"/>
+        <f>E15*F15</f>
         <v>15000</v>
       </c>
     </row>
@@ -1788,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="1"/>
+        <f>E16*F16</f>
         <v>15000</v>
       </c>
     </row>
@@ -1821,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="1"/>
+        <f>E17*F17</f>
         <v>25000</v>
       </c>
     </row>
@@ -1854,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="1"/>
+        <f>E18*F18</f>
         <v>25000</v>
       </c>
     </row>
@@ -1887,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="L19:L34" si="1">E19*F19</f>
         <v>25000</v>
       </c>
     </row>
@@ -2056,7 +2116,9 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="25" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -2064,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>30000</v>
+        <v>600</v>
       </c>
       <c r="F25" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>50</v>
@@ -2076,20 +2138,22 @@
         <v>51</v>
       </c>
       <c r="I25" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J25" s="1">
-        <v>22</v>
+        <v>1999989</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -2097,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>50000</v>
+        <v>600</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>52</v>
@@ -2109,20 +2173,22 @@
         <v>53</v>
       </c>
       <c r="I26" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J26" s="1">
-        <v>26</v>
+        <v>1999990</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1">
         <f t="shared" si="1"/>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -2130,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>50000</v>
+        <v>600</v>
       </c>
       <c r="F27" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>54</v>
@@ -2142,20 +2208,22 @@
         <v>55</v>
       </c>
       <c r="I27" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J27" s="1">
-        <v>24</v>
+        <v>1999991</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -2163,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>300000</v>
+        <v>600</v>
       </c>
       <c r="F28" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>56</v>
@@ -2175,20 +2243,22 @@
         <v>57</v>
       </c>
       <c r="I28" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J28" s="1">
-        <v>28</v>
+        <v>1999992</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -2196,10 +2266,10 @@
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>400000</v>
+        <v>1000</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>58</v>
@@ -2208,20 +2278,22 @@
         <v>59</v>
       </c>
       <c r="I29" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J29" s="1">
-        <v>30</v>
+        <v>1999001</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="1"/>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -2229,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F30" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>60</v>
@@ -2241,20 +2313,22 @@
         <v>61</v>
       </c>
       <c r="I30" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J30" s="1">
-        <v>4022</v>
+        <v>1999002</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L30" s="1">
-        <f>E30*F30</f>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <f t="shared" si="1"/>
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -2262,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F31" s="1">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>62</v>
@@ -2274,588 +2348,924 @@
         <v>63</v>
       </c>
       <c r="I31" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J31" s="1">
-        <v>4014</v>
+        <v>1999003</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L31" s="1">
-        <f>E31*F31</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <f t="shared" si="1"/>
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F32" s="1">
+        <v>33</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="1">
+        <v>11</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1999004</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="1"/>
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="1">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
         <v>5000</v>
       </c>
       <c r="F33" s="1">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I33" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J33" s="1">
-        <v>4021</v>
+        <v>1999005</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1">
-        <f>E33*F33</f>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <f t="shared" si="1"/>
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
       <c r="C34" s="1">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F34" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I34" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J34" s="1">
-        <v>4020</v>
+        <v>1999006</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <f>E34*F34</f>
-        <v>200000</v>
+        <f t="shared" si="1"/>
+        <v>66000</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C35" s="1">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>488888</v>
+        <v>30000</v>
       </c>
       <c r="F35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I35" s="1">
         <v>4</v>
       </c>
       <c r="J35" s="1">
-        <v>204</v>
+        <v>22</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <f>E35*F35</f>
-        <v>488888</v>
+        <f t="shared" ref="L35:L47" si="2">E35*F35</f>
+        <v>60000</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C36" s="1">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>3000</v>
+        <v>50000</v>
       </c>
       <c r="F36" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I36" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" s="1">
-        <v>4011</v>
+        <v>26</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <f>E36*F36</f>
-        <v>150000</v>
+        <f t="shared" si="2"/>
+        <v>50000</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C37" s="1">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="D37" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="F37" s="1">
         <v>10</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I37" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J37" s="1">
-        <v>4019</v>
+        <v>24</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <f>E37*F37</f>
-        <v>150000</v>
+        <f t="shared" si="2"/>
+        <v>500000</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C38" s="1">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="D38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="F38" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I38" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J38" s="1">
-        <v>4026</v>
+        <v>28</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <f>E38*F38</f>
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:14">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>400000</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I39" s="1">
+        <v>4</v>
+      </c>
+      <c r="J39" s="1">
+        <v>30</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="2"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C40" s="1">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="D40" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F40" s="1">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I40" s="1">
         <v>5</v>
       </c>
-      <c r="J40" s="5">
-        <v>60000001</v>
+      <c r="J40" s="1">
+        <v>4022</v>
       </c>
       <c r="K40" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" ref="L40:L49" si="2">E40*F40</f>
-        <v>100000</v>
-      </c>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:14">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C41" s="1">
-        <v>201</v>
+        <v>36</v>
       </c>
       <c r="D41" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="F41" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I41" s="1">
-        <v>5</v>
-      </c>
-      <c r="J41" s="5">
-        <v>60000002</v>
+        <v>15</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4014</v>
       </c>
       <c r="K41" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L41" s="1">
         <f t="shared" si="2"/>
-        <v>150000</v>
-      </c>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C42" s="1">
-        <v>202</v>
-      </c>
-      <c r="D42" s="1">
-        <v>4</v>
-      </c>
-      <c r="E42" s="1">
-        <v>15000</v>
-      </c>
-      <c r="F42" s="1">
-        <v>10</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="5">
-        <v>60000003</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1</v>
-      </c>
-      <c r="L42" s="1">
-        <f t="shared" si="2"/>
-        <v>150000</v>
-      </c>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="3:14">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C43" s="1">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="D43" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43" s="1">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="F43" s="1">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I43" s="1">
         <v>5</v>
       </c>
-      <c r="J43" s="5">
-        <v>60000004</v>
+      <c r="J43" s="1">
+        <v>4021</v>
       </c>
       <c r="K43" s="1">
         <v>1</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="2"/>
-        <v>125000</v>
-      </c>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="3:14">
+        <f t="shared" ref="L43:L48" si="3">E43*F43</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C44" s="1">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="D44" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" s="1">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F44" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I44" s="1">
         <v>5</v>
       </c>
-      <c r="J44" s="5">
-        <v>60000005</v>
+      <c r="J44" s="1">
+        <v>4020</v>
       </c>
       <c r="K44" s="1">
         <v>1</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="2"/>
-        <v>125000</v>
-      </c>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
+        <f t="shared" si="3"/>
+        <v>200000</v>
+      </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C45" s="1">
-        <v>205</v>
+        <v>102</v>
       </c>
       <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>488888</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I45" s="1">
         <v>4</v>
       </c>
-      <c r="E45" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F45" s="1">
-        <v>10</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="1">
-        <v>5</v>
-      </c>
-      <c r="J45" s="5">
-        <v>60000006</v>
+      <c r="J45" s="1">
+        <v>204</v>
       </c>
       <c r="K45" s="1">
         <v>1</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:12">
+        <f t="shared" si="3"/>
+        <v>488888</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C46" s="1">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="D46" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="F46" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I46" s="1">
         <v>5</v>
       </c>
-      <c r="J46" s="5">
-        <v>60000007</v>
+      <c r="J46" s="1">
+        <v>4011</v>
       </c>
       <c r="K46" s="1">
         <v>1</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:12">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C47" s="1">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="D47" s="1">
         <v>4</v>
       </c>
       <c r="E47" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="F47" s="1">
         <v>10</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>91</v>
+      <c r="G47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="I47" s="1">
         <v>5</v>
       </c>
-      <c r="J47" s="5">
-        <v>60000008</v>
+      <c r="J47" s="1">
+        <v>4019</v>
       </c>
       <c r="K47" s="1">
         <v>1</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:12">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C48" s="1">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="D48" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E48" s="1">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F48" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I48" s="1">
         <v>5</v>
       </c>
-      <c r="J48" s="5">
+      <c r="J48" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
+        <f t="shared" si="3"/>
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C50" s="1">
+        <v>200</v>
+      </c>
+      <c r="D50" s="1">
+        <v>4</v>
+      </c>
+      <c r="E50" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F50" s="1">
+        <v>5</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I50" s="1">
+        <v>5</v>
+      </c>
+      <c r="J50" s="5">
+        <v>60000001</v>
+      </c>
+      <c r="K50" s="1">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
+        <f t="shared" ref="L50:L59" si="4">E50*F50</f>
+        <v>100000</v>
+      </c>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C51" s="1">
+        <v>201</v>
+      </c>
+      <c r="D51" s="1">
+        <v>4</v>
+      </c>
+      <c r="E51" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F51" s="1">
+        <v>10</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I51" s="1">
+        <v>5</v>
+      </c>
+      <c r="J51" s="5">
+        <v>60000002</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1">
+        <f t="shared" si="4"/>
+        <v>150000</v>
+      </c>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C52" s="1">
+        <v>202</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4</v>
+      </c>
+      <c r="E52" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F52" s="1">
+        <v>10</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="5">
+        <v>60000003</v>
+      </c>
+      <c r="K52" s="1">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1">
+        <f t="shared" si="4"/>
+        <v>150000</v>
+      </c>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C53" s="1">
+        <v>203</v>
+      </c>
+      <c r="D53" s="1">
+        <v>4</v>
+      </c>
+      <c r="E53" s="1">
+        <v>25000</v>
+      </c>
+      <c r="F53" s="1">
+        <v>5</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I53" s="1">
+        <v>5</v>
+      </c>
+      <c r="J53" s="5">
+        <v>60000004</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1">
+        <f t="shared" si="4"/>
+        <v>125000</v>
+      </c>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C54" s="1">
+        <v>204</v>
+      </c>
+      <c r="D54" s="1">
+        <v>4</v>
+      </c>
+      <c r="E54" s="1">
+        <v>25000</v>
+      </c>
+      <c r="F54" s="1">
+        <v>5</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I54" s="1">
+        <v>5</v>
+      </c>
+      <c r="J54" s="5">
+        <v>60000005</v>
+      </c>
+      <c r="K54" s="1">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1">
+        <f t="shared" si="4"/>
+        <v>125000</v>
+      </c>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C55" s="1">
+        <v>205</v>
+      </c>
+      <c r="D55" s="1">
+        <v>4</v>
+      </c>
+      <c r="E55" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F55" s="1">
+        <v>10</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I55" s="1">
+        <v>5</v>
+      </c>
+      <c r="J55" s="5">
+        <v>60000006</v>
+      </c>
+      <c r="K55" s="1">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:12">
+      <c r="C56" s="1">
+        <v>206</v>
+      </c>
+      <c r="D56" s="1">
+        <v>4</v>
+      </c>
+      <c r="E56" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F56" s="1">
+        <v>10</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I56" s="1">
+        <v>5</v>
+      </c>
+      <c r="J56" s="5">
+        <v>60000007</v>
+      </c>
+      <c r="K56" s="1">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:12">
+      <c r="C57" s="1">
+        <v>207</v>
+      </c>
+      <c r="D57" s="1">
+        <v>4</v>
+      </c>
+      <c r="E57" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F57" s="1">
+        <v>10</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I57" s="1">
+        <v>5</v>
+      </c>
+      <c r="J57" s="5">
+        <v>60000008</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1</v>
+      </c>
+      <c r="L57" s="1">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:12">
+      <c r="C58" s="1">
+        <v>208</v>
+      </c>
+      <c r="D58" s="1">
+        <v>4</v>
+      </c>
+      <c r="E58" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F58" s="1">
+        <v>10</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I58" s="1">
+        <v>5</v>
+      </c>
+      <c r="J58" s="5">
         <v>60000009</v>
       </c>
-      <c r="K48" s="1">
-        <v>1</v>
-      </c>
-      <c r="L48" s="1">
-        <f t="shared" si="2"/>
+      <c r="K58" s="1">
+        <v>1</v>
+      </c>
+      <c r="L58" s="1">
+        <f t="shared" si="4"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="3:12">
-      <c r="C49" s="1">
+    <row r="59" customHeight="1" spans="3:12">
+      <c r="C59" s="1">
         <v>209</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D59" s="1">
         <v>4</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E59" s="1">
         <v>20000</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F59" s="1">
         <v>10</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="G59" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I59" s="1">
         <v>5</v>
       </c>
-      <c r="J49" s="5">
+      <c r="J59" s="5">
         <v>60000010</v>
       </c>
-      <c r="K49" s="1">
-        <v>1</v>
-      </c>
-      <c r="L49" s="1">
-        <f t="shared" si="2"/>
+      <c r="K59" s="1">
+        <v>1</v>
+      </c>
+      <c r="L59" s="1">
+        <f t="shared" si="4"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="2:3">
-      <c r="B53"/>
-      <c r="C53"/>
-    </row>
-    <row r="54" customHeight="1" spans="2:3">
-      <c r="B54"/>
-      <c r="C54"/>
-    </row>
-    <row r="55" customHeight="1" spans="2:3">
-      <c r="B55"/>
-      <c r="C55"/>
-    </row>
-    <row r="56" customHeight="1" spans="2:3">
-      <c r="B56"/>
-      <c r="C56"/>
-    </row>
-    <row r="57" customHeight="1" spans="2:3">
-      <c r="B57"/>
-      <c r="C57"/>
-    </row>
-    <row r="58" customHeight="1" spans="2:3">
-      <c r="B58"/>
-      <c r="C58"/>
-    </row>
-    <row r="59" customHeight="1" spans="2:3">
-      <c r="B59"/>
-      <c r="C59"/>
-    </row>
-    <row r="60" customHeight="1" spans="2:3">
-      <c r="B60"/>
-      <c r="C60"/>
+    <row r="63" customHeight="1" spans="2:3">
+      <c r="B63"/>
+      <c r="C63"/>
+    </row>
+    <row r="64" customHeight="1" spans="2:3">
+      <c r="B64"/>
+      <c r="C64"/>
+    </row>
+    <row r="65" customHeight="1" spans="2:3">
+      <c r="B65"/>
+      <c r="C65"/>
+    </row>
+    <row r="66" customHeight="1" spans="2:3">
+      <c r="B66"/>
+      <c r="C66"/>
+    </row>
+    <row r="67" customHeight="1" spans="2:3">
+      <c r="B67"/>
+      <c r="C67"/>
+    </row>
+    <row r="68" customHeight="1" spans="2:3">
+      <c r="B68"/>
+      <c r="C68"/>
+    </row>
+    <row r="69" customHeight="1" spans="2:3">
+      <c r="B69"/>
+      <c r="C69"/>
+    </row>
+    <row r="70" customHeight="1" spans="2:3">
+      <c r="B70"/>
+      <c r="C70"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -1518,7 +1518,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L13" si="0">E6*F6</f>
+        <f t="shared" ref="L6:L18" si="0">E6*F6</f>
         <v>5000</v>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>14</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1566,7 +1566,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>16</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1599,7 +1599,7 @@
         <v>500</v>
       </c>
       <c r="F9" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>18</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1632,7 +1632,7 @@
         <v>500</v>
       </c>
       <c r="F10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>20</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="L10" s="1">
         <f t="shared" si="0"/>
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1782,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="L14" s="1">
-        <f>E14*F14</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
     </row>
@@ -1815,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <f>E15*F15</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1">
-        <f>E16*F16</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>25000</v>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="0"/>
         <v>25000</v>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1">
         <v>600</v>
@@ -2158,7 +2158,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="1">
         <v>600</v>
@@ -2193,7 +2193,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1">
         <v>600</v>
@@ -2228,7 +2228,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="1">
         <v>600</v>
@@ -2263,7 +2263,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1">
         <v>1000</v>
@@ -2298,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="1">
         <v>2000</v>
@@ -2333,7 +2333,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1">
         <v>3000</v>
@@ -2368,7 +2368,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="1">
         <v>4000</v>
@@ -2403,7 +2403,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="1">
         <v>5000</v>
@@ -2438,7 +2438,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="1">
         <v>6000</v>
@@ -2537,7 +2537,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="1">
         <v>50000</v>
@@ -2570,7 +2570,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="1">
         <v>300000</v>
@@ -2603,7 +2603,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="1">
         <v>400000</v>
@@ -2636,7 +2636,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="1">
         <v>5000</v>

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F6" s="1">
         <v>5</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L18" si="0">E6*F6</f>
-        <v>5000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2123,7 +2123,7 @@
         <v>20</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1">
         <v>600</v>
@@ -2158,7 +2158,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1">
         <v>600</v>
@@ -2193,7 +2193,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="1">
         <v>600</v>
@@ -2228,7 +2228,7 @@
         <v>23</v>
       </c>
       <c r="D28" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="1">
         <v>600</v>
@@ -2263,7 +2263,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E29" s="1">
         <v>1000</v>
@@ -2298,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E30" s="1">
         <v>2000</v>
@@ -2333,7 +2333,7 @@
         <v>26</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E31" s="1">
         <v>3000</v>
@@ -2368,7 +2368,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" s="1">
         <v>4000</v>
@@ -2403,7 +2403,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E33" s="1">
         <v>5000</v>
@@ -2438,7 +2438,7 @@
         <v>29</v>
       </c>
       <c r="D34" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E34" s="1">
         <v>6000</v>
@@ -2537,7 +2537,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E37" s="1">
         <v>50000</v>
@@ -2570,7 +2570,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E38" s="1">
         <v>300000</v>
@@ -2603,7 +2603,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E39" s="1">
         <v>400000</v>
@@ -2636,7 +2636,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E40" s="1">
         <v>5000</v>
@@ -2669,7 +2669,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="1">
         <v>1000</v>
@@ -2702,7 +2702,7 @@
         <v>100</v>
       </c>
       <c r="D43" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E43" s="1">
         <v>5000</v>
@@ -2735,7 +2735,7 @@
         <v>101</v>
       </c>
       <c r="D44" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E44" s="1">
         <v>20000</v>
@@ -2768,7 +2768,7 @@
         <v>102</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E45" s="1">
         <v>488888</v>
@@ -2801,7 +2801,7 @@
         <v>103</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E46" s="1">
         <v>3000</v>
@@ -2834,7 +2834,7 @@
         <v>104</v>
       </c>
       <c r="D47" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E47" s="1">
         <v>15000</v>
@@ -2867,7 +2867,7 @@
         <v>105</v>
       </c>
       <c r="D48" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E48" s="1">
         <v>30000</v>
@@ -2900,7 +2900,7 @@
         <v>200</v>
       </c>
       <c r="D50" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E50" s="1">
         <v>20000</v>
@@ -2935,7 +2935,7 @@
         <v>201</v>
       </c>
       <c r="D51" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E51" s="1">
         <v>15000</v>
@@ -2970,7 +2970,7 @@
         <v>202</v>
       </c>
       <c r="D52" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E52" s="1">
         <v>15000</v>
@@ -3005,7 +3005,7 @@
         <v>203</v>
       </c>
       <c r="D53" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E53" s="1">
         <v>25000</v>
@@ -3040,7 +3040,7 @@
         <v>204</v>
       </c>
       <c r="D54" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E54" s="1">
         <v>25000</v>
@@ -3075,7 +3075,7 @@
         <v>205</v>
       </c>
       <c r="D55" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E55" s="1">
         <v>20000</v>
@@ -3108,7 +3108,7 @@
         <v>206</v>
       </c>
       <c r="D56" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E56" s="1">
         <v>20000</v>
@@ -3141,7 +3141,7 @@
         <v>207</v>
       </c>
       <c r="D57" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E57" s="1">
         <v>20000</v>
@@ -3174,7 +3174,7 @@
         <v>208</v>
       </c>
       <c r="D58" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E58" s="1">
         <v>20000</v>
@@ -3207,7 +3207,7 @@
         <v>209</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E59" s="1">
         <v>20000</v>

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="122">
   <si>
     <t>#</t>
   </si>
@@ -63,6 +63,24 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>兑换装备副本卷*100</t>
+  </si>
+  <si>
+    <t>装备副本卷</t>
+  </si>
+  <si>
+    <t>兑换BOSS挑战卷*10</t>
+  </si>
+  <si>
+    <t>BOSS挑战卷</t>
+  </si>
+  <si>
+    <t>兑换传世挑战卷*4</t>
+  </si>
+  <si>
+    <t>传世挑战卷</t>
   </si>
   <si>
     <t>兑换凤凰之羽*10</t>
@@ -1383,7 +1401,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1489,7 +1507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:12">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1497,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F6" s="1">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>12</v>
@@ -1509,17 +1527,17 @@
         <v>13</v>
       </c>
       <c r="I6" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J6" s="1">
-        <v>4008</v>
+        <v>4003</v>
       </c>
       <c r="K6" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L18" si="0">E6*F6</f>
-        <v>2500</v>
+        <f t="shared" ref="L6:L29" si="0">E6*F6</f>
+        <v>5400</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1530,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F7" s="1">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>14</v>
@@ -1545,14 +1563,14 @@
         <v>5</v>
       </c>
       <c r="J7" s="1">
-        <v>4007</v>
+        <v>4004</v>
       </c>
       <c r="K7" s="1">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1563,10 +1581,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F8" s="1">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>16</v>
@@ -1575,20 +1593,20 @@
         <v>17</v>
       </c>
       <c r="I8" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J8" s="1">
-        <v>4101</v>
+        <v>4013</v>
       </c>
       <c r="K8" s="1">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1599,7 +1617,7 @@
         <v>500</v>
       </c>
       <c r="F9" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>18</v>
@@ -1611,14 +1629,14 @@
         <v>5</v>
       </c>
       <c r="J9" s="1">
-        <v>4001</v>
+        <v>4008</v>
       </c>
       <c r="K9" s="1">
-        <v>500000</v>
+        <v>10</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1629,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>20</v>
@@ -1644,10 +1662,10 @@
         <v>5</v>
       </c>
       <c r="J10" s="1">
-        <v>4002</v>
+        <v>4007</v>
       </c>
       <c r="K10" s="1">
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="0"/>
@@ -1662,10 +1680,10 @@
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>22</v>
@@ -1677,14 +1695,14 @@
         <v>5</v>
       </c>
       <c r="J11" s="1">
-        <v>4010</v>
+        <v>4101</v>
       </c>
       <c r="K11" s="1">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="0"/>
-        <v>80000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1695,10 +1713,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F12" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>24</v>
@@ -1710,14 +1728,14 @@
         <v>5</v>
       </c>
       <c r="J12" s="1">
-        <v>4006</v>
+        <v>4001</v>
       </c>
       <c r="K12" s="1">
-        <v>200</v>
+        <v>500000</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1728,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="F13" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>26</v>
@@ -1743,17 +1761,17 @@
         <v>5</v>
       </c>
       <c r="J13" s="1">
-        <v>4102</v>
+        <v>4002</v>
       </c>
       <c r="K13" s="1">
-        <v>20</v>
+        <v>1000000</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" si="0"/>
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1761,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="F14" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>28</v>
@@ -1773,20 +1791,20 @@
         <v>29</v>
       </c>
       <c r="I14" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" s="1">
-        <v>10</v>
+        <v>4010</v>
       </c>
       <c r="K14" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:12">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1794,10 +1812,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F15" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>30</v>
@@ -1806,20 +1824,20 @@
         <v>31</v>
       </c>
       <c r="I15" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="1">
-        <v>11</v>
+        <v>4006</v>
       </c>
       <c r="K15" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:12">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1827,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>300</v>
+        <v>4000</v>
       </c>
       <c r="F16" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>32</v>
@@ -1839,20 +1857,26 @@
         <v>33</v>
       </c>
       <c r="I16" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="1">
-        <v>12</v>
+        <v>4102</v>
       </c>
       <c r="K16" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:12">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:12">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1860,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F17" s="1">
         <v>50</v>
@@ -1874,18 +1898,24 @@
       <c r="I17" s="1">
         <v>4</v>
       </c>
-      <c r="J17" s="5">
-        <v>15</v>
+      <c r="J17" s="1">
+        <v>10</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:12">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:12">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1893,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F18" s="1">
         <v>50</v>
@@ -1907,18 +1937,24 @@
       <c r="I18" s="1">
         <v>4</v>
       </c>
-      <c r="J18" s="5">
-        <v>16</v>
+      <c r="J18" s="1">
+        <v>11</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1">
         <f t="shared" si="0"/>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:12">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:12">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1926,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F19" s="1">
         <v>50</v>
@@ -1940,18 +1976,24 @@
       <c r="I19" s="1">
         <v>4</v>
       </c>
-      <c r="J19" s="5">
-        <v>17</v>
+      <c r="J19" s="1">
+        <v>12</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" ref="L19:L34" si="1">E19*F19</f>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:12">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:12">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1959,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F20" s="1">
         <v>50</v>
@@ -1971,20 +2013,26 @@
         <v>41</v>
       </c>
       <c r="I20" s="1">
-        <v>11</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1999995</v>
+        <v>4</v>
+      </c>
+      <c r="J20" s="5">
+        <v>15</v>
       </c>
       <c r="K20" s="1">
         <v>1</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:12">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:12">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1992,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F21" s="1">
         <v>50</v>
@@ -2004,20 +2052,26 @@
         <v>43</v>
       </c>
       <c r="I21" s="1">
-        <v>11</v>
-      </c>
-      <c r="J21" s="1">
-        <v>1999996</v>
+        <v>4</v>
+      </c>
+      <c r="J21" s="5">
+        <v>16</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:12">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:12">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -2025,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F22" s="1">
         <v>50</v>
@@ -2037,20 +2091,26 @@
         <v>45</v>
       </c>
       <c r="I22" s="1">
-        <v>11</v>
-      </c>
-      <c r="J22" s="1">
-        <v>1999997</v>
+        <v>4</v>
+      </c>
+      <c r="J22" s="5">
+        <v>17</v>
       </c>
       <c r="K22" s="1">
         <v>1</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:12">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -2073,17 +2133,23 @@
         <v>11</v>
       </c>
       <c r="J23" s="1">
-        <v>1999994</v>
+        <v>1999995</v>
       </c>
       <c r="K23" s="1">
         <v>1</v>
       </c>
       <c r="L23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:12">
+    <row r="24" customHeight="1" spans="1:12">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -2106,27 +2172,31 @@
         <v>11</v>
       </c>
       <c r="J24" s="1">
-        <v>1999993</v>
+        <v>1999996</v>
       </c>
       <c r="K24" s="1">
         <v>1</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
     </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
+    <row r="25" customHeight="1" spans="1:12">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="F25" s="1">
         <v>50</v>
@@ -2141,264 +2211,296 @@
         <v>11</v>
       </c>
       <c r="J25" s="1">
+        <v>1999997</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>21</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+      <c r="E26" s="1">
+        <v>300</v>
+      </c>
+      <c r="F26" s="1">
+        <v>50</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I26" s="1">
+        <v>11</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1999994</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>300</v>
+      </c>
+      <c r="F27" s="1">
+        <v>50</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="1">
+        <v>11</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1999993</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>4</v>
+      </c>
+      <c r="E28" s="1">
+        <v>600</v>
+      </c>
+      <c r="F28" s="1">
+        <v>50</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I28" s="1">
+        <v>11</v>
+      </c>
+      <c r="J28" s="1">
         <v>1999989</v>
       </c>
-      <c r="K25" s="1">
-        <v>1</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>4</v>
+      </c>
+      <c r="E29" s="1">
+        <v>600</v>
+      </c>
+      <c r="F29" s="1">
+        <v>50</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="1">
+        <v>11</v>
+      </c>
+      <c r="J29" s="1">
+        <v>1999990</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1">
+        <v>600</v>
+      </c>
+      <c r="F30" s="1">
+        <v>50</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="1">
+        <v>11</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1999991</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" ref="L22:L37" si="1">E30*F30</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1">
+        <v>600</v>
+      </c>
+      <c r="F31" s="1">
+        <v>50</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I31" s="1">
+        <v>11</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1999992</v>
+      </c>
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1">
-        <v>21</v>
-      </c>
-      <c r="D26" s="1">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1">
-        <v>600</v>
-      </c>
-      <c r="F26" s="1">
-        <v>50</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="1">
+    <row r="32" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="1">
+        <v>66</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="1">
         <v>11</v>
       </c>
-      <c r="J26" s="1">
-        <v>1999990</v>
-      </c>
-      <c r="K26" s="1">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1">
-        <v>4</v>
-      </c>
-      <c r="E27" s="1">
-        <v>600</v>
-      </c>
-      <c r="F27" s="1">
-        <v>50</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" s="1">
-        <v>11</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1999991</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="D28" s="1">
-        <v>4</v>
-      </c>
-      <c r="E28" s="1">
-        <v>600</v>
-      </c>
-      <c r="F28" s="1">
-        <v>50</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="1">
-        <v>11</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1999992</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1000</v>
-      </c>
-      <c r="F29" s="1">
-        <v>66</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I29" s="1">
-        <v>11</v>
-      </c>
-      <c r="J29" s="1">
+      <c r="J32" s="1">
         <v>1999001</v>
       </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
         <f t="shared" si="1"/>
         <v>66000</v>
       </c>
     </row>
-    <row r="30" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2000</v>
-      </c>
-      <c r="F30" s="1">
-        <v>55</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="1">
-        <v>11</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1999002</v>
-      </c>
-      <c r="K30" s="1">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" si="1"/>
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3000</v>
-      </c>
-      <c r="F31" s="1">
-        <v>44</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I31" s="1">
-        <v>11</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1999003</v>
-      </c>
-      <c r="K31" s="1">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1">
-        <f t="shared" si="1"/>
-        <v>132000</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1">
-        <v>8</v>
-      </c>
-      <c r="E32" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F32" s="1">
-        <v>33</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I32" s="1">
-        <v>11</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1999004</v>
-      </c>
-      <c r="K32" s="1">
-        <v>1</v>
-      </c>
-      <c r="L32" s="1">
-        <f t="shared" si="1"/>
-        <v>132000</v>
-      </c>
-    </row>
     <row r="33" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -2406,10 +2508,10 @@
         <v>8</v>
       </c>
       <c r="E33" s="1">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="F33" s="1">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>66</v>
@@ -2421,7 +2523,7 @@
         <v>11</v>
       </c>
       <c r="J33" s="1">
-        <v>1999005</v>
+        <v>1999002</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
@@ -2432,8 +2534,12 @@
       </c>
     </row>
     <row r="34" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -2441,10 +2547,10 @@
         <v>8</v>
       </c>
       <c r="E34" s="1">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="F34" s="1">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>68</v>
@@ -2456,28 +2562,34 @@
         <v>11</v>
       </c>
       <c r="J34" s="1">
-        <v>1999006</v>
+        <v>1999003</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" si="1"/>
-        <v>66000</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E35" s="1">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="F35" s="1">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>70</v>
@@ -2486,31 +2598,37 @@
         <v>71</v>
       </c>
       <c r="I35" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J35" s="1">
-        <v>22</v>
+        <v>1999004</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" ref="L35:L47" si="2">E35*F35</f>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <f t="shared" si="1"/>
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E36" s="1">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>72</v>
@@ -2519,31 +2637,37 @@
         <v>73</v>
       </c>
       <c r="I36" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J36" s="1">
-        <v>26</v>
+        <v>1999005</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="2"/>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <f t="shared" si="1"/>
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C37" s="1">
         <v>32</v>
       </c>
       <c r="D37" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E37" s="1">
-        <v>50000</v>
+        <v>6000</v>
       </c>
       <c r="F37" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>74</v>
@@ -2552,17 +2676,17 @@
         <v>75</v>
       </c>
       <c r="I37" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J37" s="1">
-        <v>24</v>
+        <v>1999006</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="2"/>
-        <v>500000</v>
+        <f t="shared" si="1"/>
+        <v>66000</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2570,13 +2694,13 @@
         <v>33</v>
       </c>
       <c r="D38" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="F38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>76</v>
@@ -2588,14 +2712,14 @@
         <v>4</v>
       </c>
       <c r="J38" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" si="2"/>
-        <v>300000</v>
+        <f t="shared" ref="L38:L50" si="2">E38*F38</f>
+        <v>60000</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2603,10 +2727,10 @@
         <v>34</v>
       </c>
       <c r="D39" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>400000</v>
+        <v>50000</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
@@ -2621,28 +2745,34 @@
         <v>4</v>
       </c>
       <c r="J39" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1">
         <f t="shared" si="2"/>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C40" s="1">
         <v>35</v>
       </c>
       <c r="D40" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E40" s="1">
-        <v>5000</v>
+        <v>50000</v>
       </c>
       <c r="F40" s="1">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>80</v>
@@ -2651,31 +2781,37 @@
         <v>81</v>
       </c>
       <c r="I40" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J40" s="1">
-        <v>4022</v>
+        <v>24</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L40" s="1">
         <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C41" s="1">
         <v>36</v>
       </c>
       <c r="D41" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E41" s="1">
-        <v>1000</v>
+        <v>300000</v>
       </c>
       <c r="F41" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>82</v>
@@ -2684,22 +2820,67 @@
         <v>83</v>
       </c>
       <c r="I41" s="1">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J41" s="1">
-        <v>4014</v>
+        <v>28</v>
       </c>
       <c r="K41" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L41" s="1">
         <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <v>6</v>
+      </c>
+      <c r="E42" s="1">
+        <v>400000</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I42" s="1">
+        <v>4</v>
+      </c>
+      <c r="J42" s="1">
+        <v>30</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <f t="shared" si="2"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C43" s="1">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D43" s="1">
         <v>6</v>
@@ -2711,467 +2892,532 @@
         <v>40</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I43" s="1">
         <v>5</v>
       </c>
       <c r="J43" s="1">
+        <v>4022</v>
+      </c>
+      <c r="K43" s="1">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="1">
+        <v>5</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I44" s="1">
+        <v>15</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4014</v>
+      </c>
+      <c r="K44" s="1">
+        <v>100</v>
+      </c>
+      <c r="L44" s="1">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:12">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <f>SUM(L9:L27)</f>
+        <v>318500</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>100</v>
+      </c>
+      <c r="D46" s="1">
+        <v>6</v>
+      </c>
+      <c r="E46" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F46" s="1">
+        <v>40</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
         <v>4021</v>
       </c>
-      <c r="K43" s="1">
-        <v>1</v>
-      </c>
-      <c r="L43" s="1">
-        <f t="shared" ref="L43:L48" si="3">E43*F43</f>
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <f t="shared" ref="L46:L51" si="3">E46*F46</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C44" s="1">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1">
         <v>101</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D47" s="1">
         <v>6</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E47" s="1">
         <v>20000</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F47" s="1">
         <v>10</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I44" s="1">
+      <c r="G47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I47" s="1">
         <v>5</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J47" s="1">
         <v>4020</v>
       </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
-      <c r="L44" s="1">
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
         <f t="shared" si="3"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C45" s="1">
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1">
         <v>102</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D48" s="1">
         <v>6</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E48" s="1">
         <v>488888</v>
       </c>
-      <c r="F45" s="1">
-        <v>1</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I45" s="1">
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I48" s="1">
         <v>4</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J48" s="1">
         <v>204</v>
       </c>
-      <c r="K45" s="1">
-        <v>1</v>
-      </c>
-      <c r="L45" s="1">
+      <c r="K48" s="1">
+        <v>1</v>
+      </c>
+      <c r="L48" s="1">
         <f t="shared" si="3"/>
         <v>488888</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C46" s="1">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C49" s="1">
         <v>103</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D49" s="1">
         <v>4</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E49" s="1">
         <v>3000</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F49" s="1">
         <v>50</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I46" s="1">
+      <c r="G49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I49" s="1">
         <v>5</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J49" s="1">
         <v>4011</v>
       </c>
-      <c r="K46" s="1">
-        <v>1</v>
-      </c>
-      <c r="L46" s="1">
+      <c r="K49" s="1">
+        <v>1</v>
+      </c>
+      <c r="L49" s="1">
         <f t="shared" si="3"/>
         <v>150000</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C47" s="1">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C50" s="1">
         <v>104</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D50" s="1">
         <v>8</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E50" s="1">
         <v>15000</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F50" s="1">
         <v>10</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I47" s="1">
+      <c r="G50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I50" s="1">
         <v>5</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J50" s="1">
         <v>4019</v>
       </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
-      <c r="L47" s="1">
+      <c r="K50" s="1">
+        <v>1</v>
+      </c>
+      <c r="L50" s="1">
         <f t="shared" si="3"/>
         <v>150000</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C48" s="1">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1">
         <v>105</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D51" s="1">
         <v>10</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E51" s="1">
         <v>30000</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F51" s="1">
         <v>8</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I48" s="1">
+      <c r="G51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I51" s="1">
         <v>5</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J51" s="1">
         <v>4026</v>
       </c>
-      <c r="K48" s="1">
-        <v>1</v>
-      </c>
-      <c r="L48" s="1">
+      <c r="K51" s="1">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1">
         <f t="shared" si="3"/>
         <v>240000</v>
       </c>
     </row>
-    <row r="50" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C50" s="1">
+    <row r="52" customHeight="1" spans="1:2">
+      <c r="A52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1">
         <v>200</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D53" s="1">
         <v>8</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E53" s="1">
         <v>20000</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F53" s="1">
         <v>5</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I50" s="1">
+      <c r="G53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I53" s="1">
         <v>5</v>
       </c>
-      <c r="J50" s="5">
+      <c r="J53" s="5">
         <v>60000001</v>
       </c>
-      <c r="K50" s="1">
-        <v>1</v>
-      </c>
-      <c r="L50" s="1">
-        <f t="shared" ref="L50:L59" si="4">E50*F50</f>
+      <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1">
+        <f t="shared" ref="L53:L62" si="4">E53*F53</f>
         <v>100000</v>
       </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C51" s="1">
+      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="1">
         <v>201</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D54" s="1">
         <v>8</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E54" s="1">
         <v>15000</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F54" s="1">
         <v>10</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I51" s="1">
+      <c r="G54" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I54" s="1">
         <v>5</v>
       </c>
-      <c r="J51" s="5">
+      <c r="J54" s="5">
         <v>60000002</v>
       </c>
-      <c r="K51" s="1">
-        <v>1</v>
-      </c>
-      <c r="L51" s="1">
+      <c r="K54" s="1">
+        <v>1</v>
+      </c>
+      <c r="L54" s="1">
         <f t="shared" si="4"/>
         <v>150000</v>
       </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C52" s="1">
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="1">
         <v>202</v>
       </c>
-      <c r="D52" s="1">
+      <c r="D55" s="1">
         <v>8</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E55" s="1">
         <v>15000</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F55" s="1">
         <v>10</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I52" s="1">
+      <c r="G55" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I55" s="1">
         <v>5</v>
       </c>
-      <c r="J52" s="5">
+      <c r="J55" s="5">
         <v>60000003</v>
       </c>
-      <c r="K52" s="1">
-        <v>1</v>
-      </c>
-      <c r="L52" s="1">
+      <c r="K55" s="1">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
         <f t="shared" si="4"/>
         <v>150000</v>
       </c>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C53" s="1">
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C56" s="1">
         <v>203</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D56" s="1">
         <v>8</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E56" s="1">
         <v>25000</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F56" s="1">
         <v>5</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I53" s="1">
+      <c r="G56" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I56" s="1">
         <v>5</v>
       </c>
-      <c r="J53" s="5">
+      <c r="J56" s="5">
         <v>60000004</v>
       </c>
-      <c r="K53" s="1">
-        <v>1</v>
-      </c>
-      <c r="L53" s="1">
+      <c r="K56" s="1">
+        <v>1</v>
+      </c>
+      <c r="L56" s="1">
         <f t="shared" si="4"/>
         <v>125000</v>
       </c>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C54" s="1">
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1">
         <v>204</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D57" s="1">
         <v>8</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E57" s="1">
         <v>25000</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F57" s="1">
         <v>5</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I54" s="1">
+      <c r="G57" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I57" s="1">
         <v>5</v>
       </c>
-      <c r="J54" s="5">
+      <c r="J57" s="5">
         <v>60000005</v>
       </c>
-      <c r="K54" s="1">
-        <v>1</v>
-      </c>
-      <c r="L54" s="1">
+      <c r="K57" s="1">
+        <v>1</v>
+      </c>
+      <c r="L57" s="1">
         <f t="shared" si="4"/>
         <v>125000</v>
       </c>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C55" s="1">
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C58" s="1">
         <v>205</v>
-      </c>
-      <c r="D55" s="1">
-        <v>8</v>
-      </c>
-      <c r="E55" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F55" s="1">
-        <v>10</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I55" s="1">
-        <v>5</v>
-      </c>
-      <c r="J55" s="5">
-        <v>60000006</v>
-      </c>
-      <c r="K55" s="1">
-        <v>1</v>
-      </c>
-      <c r="L55" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:12">
-      <c r="C56" s="1">
-        <v>206</v>
-      </c>
-      <c r="D56" s="1">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F56" s="1">
-        <v>10</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I56" s="1">
-        <v>5</v>
-      </c>
-      <c r="J56" s="5">
-        <v>60000007</v>
-      </c>
-      <c r="K56" s="1">
-        <v>1</v>
-      </c>
-      <c r="L56" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:12">
-      <c r="C57" s="1">
-        <v>207</v>
-      </c>
-      <c r="D57" s="1">
-        <v>8</v>
-      </c>
-      <c r="E57" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F57" s="1">
-        <v>10</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="I57" s="1">
-        <v>5</v>
-      </c>
-      <c r="J57" s="5">
-        <v>60000008</v>
-      </c>
-      <c r="K57" s="1">
-        <v>1</v>
-      </c>
-      <c r="L57" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:12">
-      <c r="C58" s="1">
-        <v>208</v>
       </c>
       <c r="D58" s="1">
         <v>8</v>
@@ -3192,7 +3438,7 @@
         <v>5</v>
       </c>
       <c r="J58" s="5">
-        <v>60000009</v>
+        <v>60000006</v>
       </c>
       <c r="K58" s="1">
         <v>1</v>
@@ -3202,9 +3448,15 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:12">
+    <row r="59" customHeight="1" spans="1:12">
+      <c r="A59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C59" s="1">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D59" s="1">
         <v>8</v>
@@ -3225,7 +3477,7 @@
         <v>5</v>
       </c>
       <c r="J59" s="5">
-        <v>60000010</v>
+        <v>60000007</v>
       </c>
       <c r="K59" s="1">
         <v>1</v>
@@ -3235,17 +3487,122 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="2:3">
-      <c r="B63"/>
-      <c r="C63"/>
-    </row>
-    <row r="64" customHeight="1" spans="2:3">
-      <c r="B64"/>
-      <c r="C64"/>
-    </row>
-    <row r="65" customHeight="1" spans="2:3">
-      <c r="B65"/>
-      <c r="C65"/>
+    <row r="60" customHeight="1" spans="1:12">
+      <c r="A60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="1">
+        <v>207</v>
+      </c>
+      <c r="D60" s="1">
+        <v>8</v>
+      </c>
+      <c r="E60" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F60" s="1">
+        <v>10</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I60" s="1">
+        <v>5</v>
+      </c>
+      <c r="J60" s="5">
+        <v>60000008</v>
+      </c>
+      <c r="K60" s="1">
+        <v>1</v>
+      </c>
+      <c r="L60" s="1">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:12">
+      <c r="A61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="1">
+        <v>208</v>
+      </c>
+      <c r="D61" s="1">
+        <v>8</v>
+      </c>
+      <c r="E61" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F61" s="1">
+        <v>10</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I61" s="1">
+        <v>5</v>
+      </c>
+      <c r="J61" s="5">
+        <v>60000009</v>
+      </c>
+      <c r="K61" s="1">
+        <v>1</v>
+      </c>
+      <c r="L61" s="1">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:12">
+      <c r="A62" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C62" s="1">
+        <v>209</v>
+      </c>
+      <c r="D62" s="1">
+        <v>8</v>
+      </c>
+      <c r="E62" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F62" s="1">
+        <v>10</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I62" s="1">
+        <v>5</v>
+      </c>
+      <c r="J62" s="5">
+        <v>60000010</v>
+      </c>
+      <c r="K62" s="1">
+        <v>1</v>
+      </c>
+      <c r="L62" s="1">
+        <f t="shared" si="4"/>
+        <v>200000</v>
+      </c>
     </row>
     <row r="66" customHeight="1" spans="2:3">
       <c r="B66"/>
@@ -3266,6 +3623,18 @@
     <row r="70" customHeight="1" spans="2:3">
       <c r="B70"/>
       <c r="C70"/>
+    </row>
+    <row r="71" customHeight="1" spans="2:3">
+      <c r="B71"/>
+      <c r="C71"/>
+    </row>
+    <row r="72" customHeight="1" spans="2:3">
+      <c r="B72"/>
+      <c r="C72"/>
+    </row>
+    <row r="73" customHeight="1" spans="2:3">
+      <c r="B73"/>
+      <c r="C73"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="122">
   <si>
     <t>#</t>
   </si>
@@ -2794,13 +2794,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C41" s="1">
         <v>36</v>
       </c>

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -131,132 +131,6 @@
     <t>高级书页</t>
   </si>
   <si>
-    <t>兑换斩仙时装包*1</t>
-  </si>
-  <si>
-    <t>斩仙时装包</t>
-  </si>
-  <si>
-    <t>兑换魔尊时装包*1</t>
-  </si>
-  <si>
-    <t>魔尊时装包</t>
-  </si>
-  <si>
-    <t>兑换幽冥时装包*1</t>
-  </si>
-  <si>
-    <t>幽冥时装包</t>
-  </si>
-  <si>
-    <t>兑换战魂时装包*1</t>
-  </si>
-  <si>
-    <t>战魂时装包</t>
-  </si>
-  <si>
-    <t>兑换法魂时装包*1</t>
-  </si>
-  <si>
-    <t>法魂时装包</t>
-  </si>
-  <si>
-    <t>兑换道魂时装包*1</t>
-  </si>
-  <si>
-    <t>道魂时装包</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之力*1</t>
-  </si>
-  <si>
-    <t>龙之力</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之智*1</t>
-  </si>
-  <si>
-    <t>龙之智</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之秘*1</t>
-  </si>
-  <si>
-    <t>龙之秘</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之御*1</t>
-  </si>
-  <si>
-    <t>龙之御</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之血*1</t>
-  </si>
-  <si>
-    <t>龙之血</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之怒*1</t>
-  </si>
-  <si>
-    <t>龙之怒</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之刀*1</t>
-  </si>
-  <si>
-    <t>龙之刀</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之杖*1</t>
-  </si>
-  <si>
-    <t>龙之杖</t>
-  </si>
-  <si>
-    <t>兑换图鉴龙之剑*1</t>
-  </si>
-  <si>
-    <t>龙之剑</t>
-  </si>
-  <si>
-    <t>兑换图鉴神鉴·白*1</t>
-  </si>
-  <si>
-    <t>神鉴·白</t>
-  </si>
-  <si>
-    <t>兑换图鉴神鉴·绿*1</t>
-  </si>
-  <si>
-    <t>神鉴·绿</t>
-  </si>
-  <si>
-    <t>兑换图鉴神鉴·蓝*1</t>
-  </si>
-  <si>
-    <t>神鉴·蓝</t>
-  </si>
-  <si>
-    <t>兑换图鉴神鉴·紫*1</t>
-  </si>
-  <si>
-    <t>神鉴·紫</t>
-  </si>
-  <si>
-    <t>兑换图鉴神鉴·橙*1</t>
-  </si>
-  <si>
-    <t>神鉴·橙</t>
-  </si>
-  <si>
-    <t>兑换图鉴神鉴·红*1</t>
-  </si>
-  <si>
-    <t>神鉴·红</t>
-  </si>
-  <si>
     <t>兑换特戒自选*1</t>
   </si>
   <si>
@@ -269,40 +143,28 @@
     <t>神技自选</t>
   </si>
   <si>
-    <t>兑换低级法宝自选*1</t>
-  </si>
-  <si>
-    <t>低级法宝自选</t>
-  </si>
-  <si>
     <t>兑换魂骨自选*1</t>
   </si>
   <si>
     <t>魂骨自选</t>
   </si>
   <si>
-    <t>兑换极矿工礼包*1</t>
-  </si>
-  <si>
-    <t>极矿工礼包</t>
-  </si>
-  <si>
     <t>兑换宠物口粮*100</t>
   </si>
   <si>
     <t>宠物口粮</t>
   </si>
   <si>
-    <t>兑换经验丹*100</t>
-  </si>
-  <si>
-    <t>经验丹</t>
-  </si>
-  <si>
-    <t>兑换改造石</t>
-  </si>
-  <si>
-    <t>改造石</t>
+    <t>兑换时装精华</t>
+  </si>
+  <si>
+    <t>时装精华</t>
+  </si>
+  <si>
+    <t>兑换超级书页</t>
+  </si>
+  <si>
+    <t>超级书页</t>
   </si>
   <si>
     <t>兑换天赋秘籍*1</t>
@@ -428,15 +290,15 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1401,26 +1263,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2566371681416" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5044247787611" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1238938053097" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8761061946903" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.50442477876106" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5044247787611" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="12:12">
+    <row r="1" customHeight="1" spans="3:12">
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1449,7 +1311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1478,7 +1340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1870,24 +1732,18 @@
         <v>40000</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:12">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C17" s="1">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>300</v>
+        <v>30000</v>
       </c>
       <c r="F17" s="1">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>34</v>
@@ -1899,34 +1755,28 @@
         <v>4</v>
       </c>
       <c r="J17" s="1">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:12">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
+        <f>E17*F17</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C18" s="1">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>300</v>
+        <v>50000</v>
       </c>
       <c r="F18" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>36</v>
@@ -1938,34 +1788,28 @@
         <v>4</v>
       </c>
       <c r="J18" s="1">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="1:12">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>0</v>
-      </c>
+        <f>E18*F18</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C19" s="1">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1">
-        <v>300</v>
+        <v>300000</v>
       </c>
       <c r="F19" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>38</v>
@@ -1977,34 +1821,28 @@
         <v>4</v>
       </c>
       <c r="J19" s="1">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:12">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
+        <f>E19*F19</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C20" s="1">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E20" s="1">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>40</v>
@@ -2013,37 +1851,31 @@
         <v>41</v>
       </c>
       <c r="I20" s="1">
-        <v>4</v>
-      </c>
-      <c r="J20" s="5">
-        <v>15</v>
+        <v>5</v>
+      </c>
+      <c r="J20" s="1">
+        <v>4022</v>
       </c>
       <c r="K20" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="0"/>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="1:12">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
+        <f>E20*F20</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C21" s="1">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E21" s="1">
-        <v>500</v>
+        <v>100000</v>
       </c>
       <c r="F21" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>42</v>
@@ -2052,37 +1884,31 @@
         <v>43</v>
       </c>
       <c r="I21" s="1">
-        <v>4</v>
-      </c>
-      <c r="J21" s="5">
-        <v>16</v>
+        <v>5</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4034</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="0"/>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:12">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
+        <f>E21*F21</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C22" s="1">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E22" s="1">
-        <v>500</v>
+        <v>150000</v>
       </c>
       <c r="F22" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>44</v>
@@ -2091,137 +1917,98 @@
         <v>45</v>
       </c>
       <c r="I22" s="1">
+        <v>5</v>
+      </c>
+      <c r="J22" s="1">
+        <v>4112</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <f>E22*F22</f>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>101</v>
+      </c>
+      <c r="D24" s="1">
+        <v>6</v>
+      </c>
+      <c r="E24" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F24" s="1">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>4020</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" ref="L23:L28" si="1">E24*F24</f>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>102</v>
+      </c>
+      <c r="D25" s="1">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1">
+        <v>488888</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="1">
         <v>4</v>
       </c>
-      <c r="J22" s="5">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1">
-        <v>1</v>
-      </c>
-      <c r="L22" s="1">
-        <f t="shared" si="0"/>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:12">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1">
-        <v>18</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>300</v>
-      </c>
-      <c r="F23" s="1">
-        <v>50</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="1">
-        <v>11</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1999995</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1</v>
-      </c>
-      <c r="L23" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:12">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="1">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-      <c r="E24" s="1">
-        <v>300</v>
-      </c>
-      <c r="F24" s="1">
-        <v>50</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I24" s="1">
-        <v>11</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1999996</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1</v>
-      </c>
-      <c r="L24" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:12">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1">
-        <v>20</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
-      </c>
-      <c r="E25" s="1">
-        <v>300</v>
-      </c>
-      <c r="F25" s="1">
-        <v>50</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I25" s="1">
-        <v>11</v>
-      </c>
       <c r="J25" s="1">
-        <v>1999997</v>
+        <v>204</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
+        <f t="shared" si="1"/>
+        <v>488888</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -2229,233 +2016,206 @@
         <v>0</v>
       </c>
       <c r="C26" s="1">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="F26" s="1">
         <v>50</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" s="1">
+        <v>5</v>
+      </c>
+      <c r="J26" s="1">
+        <v>4011</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>104</v>
+      </c>
+      <c r="D27" s="1">
+        <v>8</v>
+      </c>
+      <c r="E27" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F27" s="1">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I26" s="1">
-        <v>11</v>
-      </c>
-      <c r="J26" s="1">
-        <v>1999994</v>
-      </c>
-      <c r="K26" s="1">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1">
-        <f t="shared" si="0"/>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>105</v>
+      </c>
+      <c r="D28" s="1">
+        <v>10</v>
+      </c>
+      <c r="E28" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F28" s="1">
+        <v>8</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I28" s="1">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="1"/>
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>8</v>
+      </c>
+      <c r="E30" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="4">
+        <v>60000001</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" ref="L30:L39" si="2">E30*F30</f>
+        <v>100000</v>
+      </c>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>201</v>
+      </c>
+      <c r="D31" s="1">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1">
         <v>15000</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:12">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="1">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1">
-        <v>300</v>
-      </c>
-      <c r="F27" s="1">
-        <v>50</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I27" s="1">
-        <v>11</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1999993</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
-      <c r="L27" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1">
-        <v>23</v>
-      </c>
-      <c r="D28" s="1">
-        <v>4</v>
-      </c>
-      <c r="E28" s="1">
-        <v>600</v>
-      </c>
-      <c r="F28" s="1">
-        <v>50</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="1">
-        <v>11</v>
-      </c>
-      <c r="J28" s="1">
-        <v>1999989</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="1">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1">
-        <v>4</v>
-      </c>
-      <c r="E29" s="1">
-        <v>600</v>
-      </c>
-      <c r="F29" s="1">
-        <v>50</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="F31" s="1">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I29" s="1">
-        <v>11</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1999990</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1">
-        <v>25</v>
-      </c>
-      <c r="D30" s="1">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1">
-        <v>600</v>
-      </c>
-      <c r="F30" s="1">
-        <v>50</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="1">
-        <v>11</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1999991</v>
-      </c>
-      <c r="K30" s="1">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" ref="L22:L37" si="1">E30*F30</f>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1">
-        <v>4</v>
-      </c>
-      <c r="E31" s="1">
-        <v>600</v>
-      </c>
-      <c r="F31" s="1">
-        <v>50</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="I31" s="1">
-        <v>11</v>
-      </c>
-      <c r="J31" s="1">
-        <v>1999992</v>
+        <v>5</v>
+      </c>
+      <c r="J31" s="4">
+        <v>60000002</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="1:14">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -2463,38 +2223,40 @@
         <v>0</v>
       </c>
       <c r="C32" s="1">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="D32" s="1">
         <v>8</v>
       </c>
       <c r="E32" s="1">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="F32" s="1">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I32" s="1">
-        <v>11</v>
-      </c>
-      <c r="J32" s="1">
-        <v>1999001</v>
+        <v>5</v>
+      </c>
+      <c r="J32" s="4">
+        <v>60000003</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="1"/>
-        <v>66000</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" customHeight="1" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>150000</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="1:14">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -2502,38 +2264,40 @@
         <v>0</v>
       </c>
       <c r="C33" s="1">
-        <v>28</v>
+        <v>203</v>
       </c>
       <c r="D33" s="1">
         <v>8</v>
       </c>
       <c r="E33" s="1">
-        <v>2000</v>
+        <v>25000</v>
       </c>
       <c r="F33" s="1">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I33" s="1">
-        <v>11</v>
-      </c>
-      <c r="J33" s="1">
-        <v>1999002</v>
+        <v>5</v>
+      </c>
+      <c r="J33" s="4">
+        <v>60000004</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="1"/>
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" customHeight="1" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>125000</v>
+      </c>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="1:14">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -2541,38 +2305,40 @@
         <v>0</v>
       </c>
       <c r="C34" s="1">
-        <v>29</v>
+        <v>204</v>
       </c>
       <c r="D34" s="1">
         <v>8</v>
       </c>
       <c r="E34" s="1">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="F34" s="1">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I34" s="1">
-        <v>11</v>
-      </c>
-      <c r="J34" s="1">
-        <v>1999003</v>
+        <v>5</v>
+      </c>
+      <c r="J34" s="4">
+        <v>60000005</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="1"/>
-        <v>132000</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>125000</v>
+      </c>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -2580,38 +2346,38 @@
         <v>0</v>
       </c>
       <c r="C35" s="1">
-        <v>30</v>
+        <v>205</v>
       </c>
       <c r="D35" s="1">
         <v>8</v>
       </c>
       <c r="E35" s="1">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="F35" s="1">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I35" s="1">
-        <v>11</v>
-      </c>
-      <c r="J35" s="1">
-        <v>1999004</v>
+        <v>5</v>
+      </c>
+      <c r="J35" s="4">
+        <v>60000006</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="1"/>
-        <v>132000</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" customHeight="1" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:14">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -2619,38 +2385,38 @@
         <v>0</v>
       </c>
       <c r="C36" s="1">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="D36" s="1">
         <v>8</v>
       </c>
       <c r="E36" s="1">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F36" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I36" s="1">
-        <v>11</v>
-      </c>
-      <c r="J36" s="1">
-        <v>1999005</v>
+        <v>5</v>
+      </c>
+      <c r="J36" s="4">
+        <v>60000007</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="1"/>
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:14">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -2658,977 +2424,146 @@
         <v>0</v>
       </c>
       <c r="C37" s="1">
-        <v>32</v>
+        <v>207</v>
       </c>
       <c r="D37" s="1">
         <v>8</v>
       </c>
       <c r="E37" s="1">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="F37" s="1">
-        <v>11</v>
-      </c>
-      <c r="G37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:14">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>208</v>
+      </c>
+      <c r="D38" s="1">
+        <v>8</v>
+      </c>
+      <c r="E38" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F38" s="1">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="4">
+        <v>60000009</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:14">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>209</v>
+      </c>
+      <c r="D39" s="1">
+        <v>8</v>
+      </c>
+      <c r="E39" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I37" s="1">
-        <v>11</v>
-      </c>
-      <c r="J37" s="1">
-        <v>1999006</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="1"/>
-        <v>66000</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C38" s="1">
-        <v>33</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0</v>
-      </c>
-      <c r="E38" s="1">
-        <v>30000</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I38" s="1">
-        <v>4</v>
-      </c>
-      <c r="J38" s="1">
-        <v>22</v>
-      </c>
-      <c r="K38" s="1">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" ref="L38:L50" si="2">E38*F38</f>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C39" s="1">
-        <v>34</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <v>50000</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="I39" s="1">
-        <v>4</v>
-      </c>
-      <c r="J39" s="1">
-        <v>26</v>
+        <v>5</v>
+      </c>
+      <c r="J39" s="4">
+        <v>60000010</v>
       </c>
       <c r="K39" s="1">
         <v>1</v>
       </c>
       <c r="L39" s="1">
         <f t="shared" si="2"/>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C40" s="1">
-        <v>35</v>
-      </c>
-      <c r="D40" s="1">
-        <v>10</v>
-      </c>
-      <c r="E40" s="1">
-        <v>50000</v>
-      </c>
-      <c r="F40" s="1">
-        <v>10</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I40" s="1">
-        <v>4</v>
-      </c>
-      <c r="J40" s="1">
-        <v>24</v>
-      </c>
-      <c r="K40" s="1">
-        <v>1</v>
-      </c>
-      <c r="L40" s="1">
-        <f t="shared" si="2"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C41" s="1">
-        <v>36</v>
-      </c>
-      <c r="D41" s="1">
-        <v>6</v>
-      </c>
-      <c r="E41" s="1">
-        <v>300000</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I41" s="1">
-        <v>4</v>
-      </c>
-      <c r="J41" s="1">
-        <v>28</v>
-      </c>
-      <c r="K41" s="1">
-        <v>1</v>
-      </c>
-      <c r="L41" s="1">
-        <f t="shared" si="2"/>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="1">
-        <v>37</v>
-      </c>
-      <c r="D42" s="1">
-        <v>6</v>
-      </c>
-      <c r="E42" s="1">
-        <v>400000</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I42" s="1">
-        <v>4</v>
-      </c>
-      <c r="J42" s="1">
-        <v>30</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1</v>
-      </c>
-      <c r="L42" s="1">
-        <f t="shared" si="2"/>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C43" s="1">
-        <v>38</v>
-      </c>
-      <c r="D43" s="1">
-        <v>6</v>
-      </c>
-      <c r="E43" s="1">
-        <v>5000</v>
-      </c>
-      <c r="F43" s="1">
-        <v>40</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="1">
-        <v>4022</v>
-      </c>
-      <c r="K43" s="1">
-        <v>100</v>
-      </c>
-      <c r="L43" s="1">
-        <f t="shared" si="2"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C44" s="1">
-        <v>39</v>
-      </c>
-      <c r="D44" s="1">
-        <v>4</v>
-      </c>
-      <c r="E44" s="1">
-        <v>1000</v>
-      </c>
-      <c r="F44" s="1">
-        <v>5</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I44" s="1">
-        <v>15</v>
-      </c>
-      <c r="J44" s="1">
-        <v>4014</v>
-      </c>
-      <c r="K44" s="1">
-        <v>100</v>
-      </c>
-      <c r="L44" s="1">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:12">
-      <c r="A45" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <f>SUM(L9:L27)</f>
-        <v>318500</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C46" s="1">
-        <v>100</v>
-      </c>
-      <c r="D46" s="1">
-        <v>6</v>
-      </c>
-      <c r="E46" s="1">
-        <v>5000</v>
-      </c>
-      <c r="F46" s="1">
-        <v>40</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
-        <v>4021</v>
-      </c>
-      <c r="K46" s="1">
-        <v>1</v>
-      </c>
-      <c r="L46" s="1">
-        <f t="shared" ref="L46:L51" si="3">E46*F46</f>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" s="1">
-        <v>101</v>
-      </c>
-      <c r="D47" s="1">
-        <v>6</v>
-      </c>
-      <c r="E47" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F47" s="1">
-        <v>10</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I47" s="1">
-        <v>5</v>
-      </c>
-      <c r="J47" s="1">
-        <v>4020</v>
-      </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
-      <c r="L47" s="1">
-        <f t="shared" si="3"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C48" s="1">
-        <v>102</v>
-      </c>
-      <c r="D48" s="1">
-        <v>6</v>
-      </c>
-      <c r="E48" s="1">
-        <v>488888</v>
-      </c>
-      <c r="F48" s="1">
-        <v>1</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I48" s="1">
-        <v>4</v>
-      </c>
-      <c r="J48" s="1">
-        <v>204</v>
-      </c>
-      <c r="K48" s="1">
-        <v>1</v>
-      </c>
-      <c r="L48" s="1">
-        <f t="shared" si="3"/>
-        <v>488888</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C49" s="1">
-        <v>103</v>
-      </c>
-      <c r="D49" s="1">
-        <v>4</v>
-      </c>
-      <c r="E49" s="1">
-        <v>3000</v>
-      </c>
-      <c r="F49" s="1">
-        <v>50</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="I49" s="1">
-        <v>5</v>
-      </c>
-      <c r="J49" s="1">
-        <v>4011</v>
-      </c>
-      <c r="K49" s="1">
-        <v>1</v>
-      </c>
-      <c r="L49" s="1">
-        <f t="shared" si="3"/>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C50" s="1">
-        <v>104</v>
-      </c>
-      <c r="D50" s="1">
-        <v>8</v>
-      </c>
-      <c r="E50" s="1">
-        <v>15000</v>
-      </c>
-      <c r="F50" s="1">
-        <v>10</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I50" s="1">
-        <v>5</v>
-      </c>
-      <c r="J50" s="1">
-        <v>4019</v>
-      </c>
-      <c r="K50" s="1">
-        <v>1</v>
-      </c>
-      <c r="L50" s="1">
-        <f t="shared" si="3"/>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C51" s="1">
-        <v>105</v>
-      </c>
-      <c r="D51" s="1">
-        <v>10</v>
-      </c>
-      <c r="E51" s="1">
-        <v>30000</v>
-      </c>
-      <c r="F51" s="1">
-        <v>8</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I51" s="1">
-        <v>5</v>
-      </c>
-      <c r="J51" s="1">
-        <v>4026</v>
-      </c>
-      <c r="K51" s="1">
-        <v>1</v>
-      </c>
-      <c r="L51" s="1">
-        <f t="shared" si="3"/>
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:2">
-      <c r="A52" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C53" s="1">
-        <v>200</v>
-      </c>
-      <c r="D53" s="1">
-        <v>8</v>
-      </c>
-      <c r="E53" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F53" s="1">
-        <v>5</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I53" s="1">
-        <v>5</v>
-      </c>
-      <c r="J53" s="5">
-        <v>60000001</v>
-      </c>
-      <c r="K53" s="1">
-        <v>1</v>
-      </c>
-      <c r="L53" s="1">
-        <f t="shared" ref="L53:L62" si="4">E53*F53</f>
-        <v>100000</v>
-      </c>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="1">
-        <v>201</v>
-      </c>
-      <c r="D54" s="1">
-        <v>8</v>
-      </c>
-      <c r="E54" s="1">
-        <v>15000</v>
-      </c>
-      <c r="F54" s="1">
-        <v>10</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I54" s="1">
-        <v>5</v>
-      </c>
-      <c r="J54" s="5">
-        <v>60000002</v>
-      </c>
-      <c r="K54" s="1">
-        <v>1</v>
-      </c>
-      <c r="L54" s="1">
-        <f t="shared" si="4"/>
-        <v>150000</v>
-      </c>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="1">
-        <v>202</v>
-      </c>
-      <c r="D55" s="1">
-        <v>8</v>
-      </c>
-      <c r="E55" s="1">
-        <v>15000</v>
-      </c>
-      <c r="F55" s="1">
-        <v>10</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I55" s="1">
-        <v>5</v>
-      </c>
-      <c r="J55" s="5">
-        <v>60000003</v>
-      </c>
-      <c r="K55" s="1">
-        <v>1</v>
-      </c>
-      <c r="L55" s="1">
-        <f t="shared" si="4"/>
-        <v>150000</v>
-      </c>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C56" s="1">
-        <v>203</v>
-      </c>
-      <c r="D56" s="1">
-        <v>8</v>
-      </c>
-      <c r="E56" s="1">
-        <v>25000</v>
-      </c>
-      <c r="F56" s="1">
-        <v>5</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I56" s="1">
-        <v>5</v>
-      </c>
-      <c r="J56" s="5">
-        <v>60000004</v>
-      </c>
-      <c r="K56" s="1">
-        <v>1</v>
-      </c>
-      <c r="L56" s="1">
-        <f t="shared" si="4"/>
-        <v>125000</v>
-      </c>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-    </row>
-    <row r="57" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C57" s="1">
-        <v>204</v>
-      </c>
-      <c r="D57" s="1">
-        <v>8</v>
-      </c>
-      <c r="E57" s="1">
-        <v>25000</v>
-      </c>
-      <c r="F57" s="1">
-        <v>5</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I57" s="1">
-        <v>5</v>
-      </c>
-      <c r="J57" s="5">
-        <v>60000005</v>
-      </c>
-      <c r="K57" s="1">
-        <v>1</v>
-      </c>
-      <c r="L57" s="1">
-        <f t="shared" si="4"/>
-        <v>125000</v>
-      </c>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C58" s="1">
-        <v>205</v>
-      </c>
-      <c r="D58" s="1">
-        <v>8</v>
-      </c>
-      <c r="E58" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F58" s="1">
-        <v>10</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I58" s="1">
-        <v>5</v>
-      </c>
-      <c r="J58" s="5">
-        <v>60000006</v>
-      </c>
-      <c r="K58" s="1">
-        <v>1</v>
-      </c>
-      <c r="L58" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:12">
-      <c r="A59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="1">
-        <v>206</v>
-      </c>
-      <c r="D59" s="1">
-        <v>8</v>
-      </c>
-      <c r="E59" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F59" s="1">
-        <v>10</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I59" s="1">
-        <v>5</v>
-      </c>
-      <c r="J59" s="5">
-        <v>60000007</v>
-      </c>
-      <c r="K59" s="1">
-        <v>1</v>
-      </c>
-      <c r="L59" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="1:12">
-      <c r="A60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="1">
-        <v>207</v>
-      </c>
-      <c r="D60" s="1">
-        <v>8</v>
-      </c>
-      <c r="E60" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F60" s="1">
-        <v>10</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="I60" s="1">
-        <v>5</v>
-      </c>
-      <c r="J60" s="5">
-        <v>60000008</v>
-      </c>
-      <c r="K60" s="1">
-        <v>1</v>
-      </c>
-      <c r="L60" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:12">
-      <c r="A61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C61" s="1">
-        <v>208</v>
-      </c>
-      <c r="D61" s="1">
-        <v>8</v>
-      </c>
-      <c r="E61" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F61" s="1">
-        <v>10</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I61" s="1">
-        <v>5</v>
-      </c>
-      <c r="J61" s="5">
-        <v>60000009</v>
-      </c>
-      <c r="K61" s="1">
-        <v>1</v>
-      </c>
-      <c r="L61" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:12">
-      <c r="A62" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C62" s="1">
-        <v>209</v>
-      </c>
-      <c r="D62" s="1">
-        <v>8</v>
-      </c>
-      <c r="E62" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F62" s="1">
-        <v>10</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I62" s="1">
-        <v>5</v>
-      </c>
-      <c r="J62" s="5">
-        <v>60000010</v>
-      </c>
-      <c r="K62" s="1">
-        <v>1</v>
-      </c>
-      <c r="L62" s="1">
-        <f t="shared" si="4"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="2:3">
-      <c r="B66"/>
-      <c r="C66"/>
-    </row>
-    <row r="67" customHeight="1" spans="2:3">
-      <c r="B67"/>
-      <c r="C67"/>
-    </row>
-    <row r="68" customHeight="1" spans="2:3">
-      <c r="B68"/>
-      <c r="C68"/>
-    </row>
-    <row r="69" customHeight="1" spans="2:3">
-      <c r="B69"/>
-      <c r="C69"/>
-    </row>
-    <row r="70" customHeight="1" spans="2:3">
-      <c r="B70"/>
-      <c r="C70"/>
-    </row>
-    <row r="71" customHeight="1" spans="2:3">
-      <c r="B71"/>
-      <c r="C71"/>
-    </row>
-    <row r="72" customHeight="1" spans="2:3">
-      <c r="B72"/>
-      <c r="C72"/>
-    </row>
-    <row r="73" customHeight="1" spans="2:3">
-      <c r="B73"/>
-      <c r="C73"/>
+    <row r="43" customHeight="1" spans="1:14">
+      <c r="B43"/>
+      <c r="C43"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:14">
+      <c r="B44"/>
+      <c r="C44"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:14">
+      <c r="B45"/>
+      <c r="C45"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:14">
+      <c r="B46"/>
+      <c r="C46"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:14">
+      <c r="B47"/>
+      <c r="C47"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:14">
+      <c r="B48"/>
+      <c r="C48"/>
+    </row>
+    <row r="49" customHeight="1" spans="2:3">
+      <c r="B49"/>
+      <c r="C49"/>
+    </row>
+    <row r="50" customHeight="1" spans="2:3">
+      <c r="B50"/>
+      <c r="C50"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -171,12 +171,6 @@
   </si>
   <si>
     <t>天赋秘籍</t>
-  </si>
-  <si>
-    <t>兑换红宠自选</t>
-  </si>
-  <si>
-    <t>红宠自选</t>
   </si>
   <si>
     <t>兑换红装精华*1</t>
@@ -1263,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1761,7 +1755,7 @@
         <v>1</v>
       </c>
       <c r="L17" s="1">
-        <f>E17*F17</f>
+        <f t="shared" si="0"/>
         <v>60000</v>
       </c>
     </row>
@@ -1794,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="L18" s="1">
-        <f>E18*F18</f>
+        <f t="shared" si="0"/>
         <v>50000</v>
       </c>
     </row>
@@ -1827,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="L19" s="1">
-        <f>E19*F19</f>
+        <f t="shared" si="0"/>
         <v>300000</v>
       </c>
     </row>
@@ -1860,7 +1854,7 @@
         <v>100</v>
       </c>
       <c r="L20" s="1">
-        <f>E20*F20</f>
+        <f t="shared" si="0"/>
         <v>500000</v>
       </c>
     </row>
@@ -1893,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="1">
-        <f>E21*F21</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
     </row>
@@ -1926,28 +1920,22 @@
         <v>1</v>
       </c>
       <c r="L22" s="1">
-        <f>E22*F22</f>
+        <f t="shared" si="0"/>
         <v>150000</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C24" s="1">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="D24" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1">
         <v>20000</v>
       </c>
       <c r="F24" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>46</v>
@@ -1965,28 +1953,22 @@
         <v>1</v>
       </c>
       <c r="L24" s="1">
-        <f t="shared" ref="L23:L28" si="1">E24*F24</f>
-        <v>200000</v>
+        <f>E24*F24</f>
+        <v>400000</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C25" s="1">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="D25" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1">
-        <v>488888</v>
+        <v>3000</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>48</v>
@@ -1995,37 +1977,31 @@
         <v>49</v>
       </c>
       <c r="I25" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J25" s="1">
-        <v>204</v>
+        <v>4011</v>
       </c>
       <c r="K25" s="1">
         <v>1</v>
       </c>
       <c r="L25" s="1">
-        <f t="shared" si="1"/>
-        <v>488888</v>
+        <f>E25*F25</f>
+        <v>150000</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C26" s="1">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" s="1">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="F26" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>50</v>
@@ -2037,181 +2013,177 @@
         <v>5</v>
       </c>
       <c r="J26" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="K26" s="1">
         <v>1</v>
       </c>
       <c r="L26" s="1">
+        <f>E26*F26</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C27" s="1">
+        <v>43</v>
+      </c>
+      <c r="D27" s="1">
+        <v>10</v>
+      </c>
+      <c r="E27" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F27" s="1">
+        <v>20</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <f>E27*F27</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:14">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I29" s="1">
+        <v>5</v>
+      </c>
+      <c r="J29" s="4">
+        <v>60000001</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" ref="L29:L38" si="1">E29*F29</f>
+        <v>100000</v>
+      </c>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>201</v>
+      </c>
+      <c r="D30" s="1">
+        <v>8</v>
+      </c>
+      <c r="E30" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F30" s="1">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="4">
+        <v>60000002</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="1">
-        <v>104</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>202</v>
+      </c>
+      <c r="D31" s="1">
         <v>8</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E31" s="1">
         <v>15000</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F31" s="1">
         <v>10</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I27" s="1">
-        <v>5</v>
-      </c>
-      <c r="J27" s="1">
-        <v>4019</v>
-      </c>
-      <c r="K27" s="1">
+      <c r="G31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="4">
+        <v>60000003</v>
+      </c>
+      <c r="K31" s="1">
         <v>1</v>
       </c>
-      <c r="L27" s="1">
+      <c r="L31" s="1">
         <f t="shared" si="1"/>
         <v>150000</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1">
-        <v>105</v>
-      </c>
-      <c r="D28" s="1">
-        <v>10</v>
-      </c>
-      <c r="E28" s="1">
-        <v>30000</v>
-      </c>
-      <c r="F28" s="1">
-        <v>8</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I28" s="1">
-        <v>5</v>
-      </c>
-      <c r="J28" s="1">
-        <v>4026</v>
-      </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
-      <c r="L28" s="1">
-        <f t="shared" si="1"/>
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:14">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1">
-        <v>200</v>
-      </c>
-      <c r="D30" s="1">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F30" s="1">
-        <v>5</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I30" s="1">
-        <v>5</v>
-      </c>
-      <c r="J30" s="4">
-        <v>60000001</v>
-      </c>
-      <c r="K30" s="1">
-        <v>1</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" ref="L30:L39" si="2">E30*F30</f>
-        <v>100000</v>
-      </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1">
-        <v>201</v>
-      </c>
-      <c r="D31" s="1">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1">
-        <v>15000</v>
-      </c>
-      <c r="F31" s="1">
-        <v>10</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" s="1">
-        <v>5</v>
-      </c>
-      <c r="J31" s="4">
-        <v>60000002</v>
-      </c>
-      <c r="K31" s="1">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1">
-        <f t="shared" si="2"/>
-        <v>150000</v>
-      </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
     </row>
@@ -2223,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="C32" s="1">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D32" s="1">
         <v>8</v>
       </c>
       <c r="E32" s="1">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="F32" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>60</v>
@@ -2244,14 +2216,14 @@
         <v>5</v>
       </c>
       <c r="J32" s="4">
-        <v>60000003</v>
+        <v>60000004</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="2"/>
-        <v>150000</v>
+        <f t="shared" si="1"/>
+        <v>125000</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -2264,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="1">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D33" s="1">
         <v>8</v>
@@ -2285,19 +2257,19 @@
         <v>5</v>
       </c>
       <c r="J33" s="4">
-        <v>60000004</v>
+        <v>60000005</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>125000</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" customFormat="1" customHeight="1" spans="1:14">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -2305,16 +2277,16 @@
         <v>0</v>
       </c>
       <c r="C34" s="1">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D34" s="1">
         <v>8</v>
       </c>
       <c r="E34" s="1">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F34" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>64</v>
@@ -2326,19 +2298,17 @@
         <v>5</v>
       </c>
       <c r="J34" s="4">
-        <v>60000005</v>
+        <v>60000006</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="2"/>
-        <v>125000</v>
-      </c>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <f t="shared" si="1"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:14">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -2346,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="1">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D35" s="1">
         <v>8</v>
@@ -2367,13 +2337,13 @@
         <v>5</v>
       </c>
       <c r="J35" s="4">
-        <v>60000006</v>
+        <v>60000007</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>200000</v>
       </c>
     </row>
@@ -2385,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="1">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D36" s="1">
         <v>8</v>
@@ -2396,23 +2366,23 @@
       <c r="F36" s="1">
         <v>10</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I36" s="1">
         <v>5</v>
       </c>
       <c r="J36" s="4">
-        <v>60000007</v>
+        <v>60000008</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>200000</v>
       </c>
     </row>
@@ -2424,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="1">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D37" s="1">
         <v>8</v>
@@ -2435,23 +2405,23 @@
       <c r="F37" s="1">
         <v>10</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="1" t="s">
         <v>71</v>
       </c>
       <c r="I37" s="1">
         <v>5</v>
       </c>
       <c r="J37" s="4">
-        <v>60000008</v>
+        <v>60000009</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>200000</v>
       </c>
     </row>
@@ -2463,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="1">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D38" s="1">
         <v>8</v>
@@ -2484,54 +2454,19 @@
         <v>5</v>
       </c>
       <c r="J38" s="4">
-        <v>60000009</v>
+        <v>60000010</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:14">
-      <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
-        <v>209</v>
-      </c>
-      <c r="D39" s="1">
-        <v>8</v>
-      </c>
-      <c r="E39" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F39" s="1">
-        <v>10</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
-      <c r="J39" s="4">
-        <v>60000010</v>
-      </c>
-      <c r="K39" s="1">
-        <v>1</v>
-      </c>
-      <c r="L39" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
+    <row r="42" customHeight="1" spans="1:14">
+      <c r="B42"/>
+      <c r="C42"/>
     </row>
     <row r="43" customHeight="1" spans="1:14">
       <c r="B43"/>
@@ -2560,10 +2495,6 @@
     <row r="49" customHeight="1" spans="2:3">
       <c r="B49"/>
       <c r="C49"/>
-    </row>
-    <row r="50" customHeight="1" spans="2:3">
-      <c r="B50"/>
-      <c r="C50"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -1833,7 +1833,7 @@
         <v>6</v>
       </c>
       <c r="E20" s="1">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="1">
         <v>100</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="L20" s="1">
         <f t="shared" si="0"/>
-        <v>500000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -189,6 +189,12 @@
   </si>
   <si>
     <t>暗金精华</t>
+  </si>
+  <si>
+    <t>兑换极矿工礼包*1</t>
+  </si>
+  <si>
+    <t>极矿工礼包</t>
   </si>
   <si>
     <t>兑换攻击宝石</t>
@@ -1257,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1953,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="1">
-        <f>E24*F24</f>
+        <f t="shared" ref="L24:L28" si="1">E24*F24</f>
         <v>400000</v>
       </c>
     </row>
@@ -1986,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="L25" s="1">
-        <f>E25*F25</f>
+        <f t="shared" si="1"/>
         <v>150000</v>
       </c>
     </row>
@@ -2019,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="L26" s="1">
-        <f>E26*F26</f>
+        <f t="shared" si="1"/>
         <v>300000</v>
       </c>
     </row>
@@ -2052,58 +2058,50 @@
         <v>1</v>
       </c>
       <c r="L27" s="1">
-        <f>E27*F27</f>
+        <f t="shared" si="1"/>
         <v>600000</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:14">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:14">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C28" s="1">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>150000</v>
+      </c>
+      <c r="F28" s="1">
+        <v>2</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I28" s="1">
+        <v>4</v>
+      </c>
+      <c r="J28" s="1">
+        <v>30</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="1">
-        <v>200</v>
-      </c>
-      <c r="D29" s="1">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F29" s="1">
-        <v>5</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I29" s="1">
-        <v>5</v>
-      </c>
-      <c r="J29" s="4">
-        <v>60000001</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
-      <c r="L29" s="1">
-        <f t="shared" ref="L29:L38" si="1">E29*F29</f>
-        <v>100000</v>
-      </c>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
     </row>
     <row r="30" customFormat="1" customHeight="1" spans="1:14">
       <c r="A30" s="1" t="s">
@@ -2113,16 +2111,16 @@
         <v>0</v>
       </c>
       <c r="C30" s="1">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D30" s="1">
         <v>8</v>
       </c>
       <c r="E30" s="1">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="F30" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>56</v>
@@ -2134,14 +2132,14 @@
         <v>5</v>
       </c>
       <c r="J30" s="4">
-        <v>60000002</v>
+        <v>60000001</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="1"/>
-        <v>150000</v>
+        <f t="shared" ref="L30:L39" si="2">E30*F30</f>
+        <v>100000</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
@@ -2154,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D31" s="1">
         <v>8</v>
@@ -2175,13 +2173,13 @@
         <v>5</v>
       </c>
       <c r="J31" s="4">
-        <v>60000003</v>
+        <v>60000002</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>150000</v>
       </c>
       <c r="M31" s="1"/>
@@ -2195,16 +2193,16 @@
         <v>0</v>
       </c>
       <c r="C32" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" s="1">
         <v>8</v>
       </c>
       <c r="E32" s="1">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="F32" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>60</v>
@@ -2216,14 +2214,14 @@
         <v>5</v>
       </c>
       <c r="J32" s="4">
-        <v>60000004</v>
+        <v>60000003</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="1"/>
-        <v>125000</v>
+        <f t="shared" si="2"/>
+        <v>150000</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -2236,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" s="1">
         <v>8</v>
@@ -2257,19 +2255,19 @@
         <v>5</v>
       </c>
       <c r="J33" s="4">
-        <v>60000005</v>
+        <v>60000004</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125000</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="34" customFormat="1" customHeight="1" spans="1:14">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -2277,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="C34" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D34" s="1">
         <v>8</v>
       </c>
       <c r="E34" s="1">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="F34" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>64</v>
@@ -2298,17 +2296,19 @@
         <v>5</v>
       </c>
       <c r="J34" s="4">
-        <v>60000006</v>
+        <v>60000005</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="1"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:14">
+        <f t="shared" si="2"/>
+        <v>125000</v>
+      </c>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D35" s="1">
         <v>8</v>
@@ -2337,13 +2337,13 @@
         <v>5</v>
       </c>
       <c r="J35" s="4">
-        <v>60000007</v>
+        <v>60000006</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200000</v>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D36" s="1">
         <v>8</v>
@@ -2366,23 +2366,23 @@
       <c r="F36" s="1">
         <v>10</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="1" t="s">
         <v>69</v>
       </c>
       <c r="I36" s="1">
         <v>5</v>
       </c>
       <c r="J36" s="4">
-        <v>60000008</v>
+        <v>60000007</v>
       </c>
       <c r="K36" s="1">
         <v>1</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200000</v>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D37" s="1">
         <v>8</v>
@@ -2405,23 +2405,23 @@
       <c r="F37" s="1">
         <v>10</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="5" t="s">
         <v>71</v>
       </c>
       <c r="I37" s="1">
         <v>5</v>
       </c>
       <c r="J37" s="4">
-        <v>60000009</v>
+        <v>60000008</v>
       </c>
       <c r="K37" s="1">
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>200000</v>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D38" s="1">
         <v>8</v>
@@ -2454,19 +2454,54 @@
         <v>5</v>
       </c>
       <c r="J38" s="4">
+        <v>60000009</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:14">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>209</v>
+      </c>
+      <c r="D39" s="1">
+        <v>8</v>
+      </c>
+      <c r="E39" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="4">
         <v>60000010</v>
       </c>
-      <c r="K38" s="1">
-        <v>1</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" si="1"/>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="2"/>
         <v>200000</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:14">
-      <c r="B42"/>
-      <c r="C42"/>
     </row>
     <row r="43" customHeight="1" spans="1:14">
       <c r="B43"/>
@@ -2495,6 +2530,10 @@
     <row r="49" customHeight="1" spans="2:3">
       <c r="B49"/>
       <c r="C49"/>
+    </row>
+    <row r="50" customHeight="1" spans="2:3">
+      <c r="B50"/>
+      <c r="C50"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveWeekConfig.xlsx
+++ b/Excel/FestiveWeekConfig.xlsx
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="1">
         <v>20</v>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" si="0"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1806,7 +1806,7 @@
         <v>6</v>
       </c>
       <c r="E19" s="1">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="F19" s="1">
         <v>1</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L19" s="1">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
